--- a/apparati.xlsx
+++ b/apparati.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Apparati" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Movimenti" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apparati" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimenti" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -456,7 +456,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H1000"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.67" customWidth="1" style="3" min="1" max="2"/>
     <col width="24.73" customWidth="1" style="3" min="3" max="3"/>
@@ -502,7 +502,7 @@
           <t>Data_ultimo_movimento</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Alias</t>
         </is>
@@ -527,26 +527,18 @@
           <t>Faunistica</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>In carico</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Podestà</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-07-12 17:19:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>pod21</t>
-        </is>
-      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 11:46:08</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="13.8" customHeight="1" s="4">
       <c r="A3" s="5" t="inlineStr">
@@ -578,7 +570,7 @@
           <t>2026-07-12 17:18:47</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="13.8" customHeight="1" s="4">
       <c r="A4" s="5" t="inlineStr">
@@ -5468,8 +5460,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.67" customWidth="1" style="3" min="1" max="1025"/>
   </cols>
@@ -5505,7 +5497,7 @@
           <t>Operatore</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Alias</t>
         </is>
@@ -5544,70 +5536,107 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-07-12 17:18:47</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>TLC – 02</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Sepura</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Scarico</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jacopo Marzio</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Operatore</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-07-12 17:19:00</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>TLC – 01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Sepura</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Carico</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Podestà</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Operatore</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>pod21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-18 11:46:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TLC - 01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sepura</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Scarico</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Podestà</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Operatore</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>pod21</t>
         </is>
